--- a/materials/設計ドキュメント.xlsx
+++ b/materials/設計ドキュメント.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ehimeuniv-my.sharepoint.com/personal/m520391m_mails_cc_ehime-u_ac_jp/Documents/授業資料/ソフトウェア工学Ⅱ/第５回/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\篠崎心寧\Desktop\team03\materials\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="17" documentId="6_{96CA27AD-3E83-4FA0-B80F-52050CF050FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EAA823F3-F23F-4D77-A5FC-C2C3BBA856E5}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D084DE1C-4937-4B72-A096-298D6A45EB07}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{8691A593-23F5-4A86-9C44-944ADFFAF4A8}"/>
+    <workbookView xWindow="9510" yWindow="0" windowWidth="9780" windowHeight="10170" xr2:uid="{8691A593-23F5-4A86-9C44-944ADFFAF4A8}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="39">
   <si>
     <t>クラス名</t>
     <rPh sb="3" eb="4">
@@ -418,6 +418,34 @@
   </si>
   <si>
     <t>保存時はCompanyRepository（別行）のadd／updateを呼び出す想定。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>入力（InputField）</t>
+    <rPh sb="0" eb="2">
+      <t>ニュウリョク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>表示位置とサイズ（x, y, w, h）
+ラベル文字列（label）
+入力された値（value）
+フォーカス中かどうか（isActive）</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>入力欄を描画する（display）
+クリック位置が自分の範囲内か判定する（isInside）
+クリックされたらフォーカス状態を切り替える（handleClick）
+キー入力をvalueに反映する（handleKey）</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ScreenAddEdit実装時、企業名・URL・ID・各締切日など10個の入力欄で
+同じ処理を繰り返すことに気づき、共通クラスとして分離した。
+特定の画面に属さない汎用部品のため、カレンダー画面の「予定を追加」欄など
+他の画面でも再利用できる可能性がある。</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -450,7 +478,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="5">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -507,6 +535,17 @@
       <top style="thin">
         <color indexed="64"/>
       </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
       <bottom/>
       <diagonal/>
     </border>
@@ -535,6 +574,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
@@ -544,11 +586,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -565,10 +604,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -888,17 +923,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{22421680-BCA4-49CB-9187-F4BA601714C9}">
-  <dimension ref="A1:F19"/>
-  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
+  <dimension ref="A1:E19"/>
+  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
-    <col min="1" max="1" width="23.19921875" customWidth="1"/>
-    <col min="2" max="2" width="9.8984375" customWidth="1"/>
-    <col min="3" max="3" width="29.8984375" customWidth="1"/>
+    <col min="1" max="1" width="23.1640625" customWidth="1"/>
+    <col min="2" max="2" width="9.9140625" customWidth="1"/>
+    <col min="3" max="3" width="29.9140625" customWidth="1"/>
     <col min="4" max="4" width="30" customWidth="1"/>
-    <col min="5" max="5" width="63.19921875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="63.1640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -915,7 +950,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:6" ht="92.25" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:5" ht="92.25" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" s="1" t="s">
         <v>5</v>
       </c>
@@ -930,7 +965,7 @@
       </c>
       <c r="E2" s="1"/>
     </row>
-    <row r="3" spans="1:6" ht="216" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:5" ht="216" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" s="1" t="s">
         <v>9</v>
       </c>
@@ -947,7 +982,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="4" spans="1:6" ht="180" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:5" ht="180" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" s="1" t="s">
         <v>13</v>
       </c>
@@ -964,7 +999,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="5" spans="1:6" ht="50.25" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:5" ht="50.25" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" s="2" t="s">
         <v>17</v>
       </c>
@@ -974,93 +1009,92 @@
       <c r="C5" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="D5" s="10" t="s">
+      <c r="D5" s="6" t="s">
         <v>19</v>
       </c>
       <c r="E5" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="F5" s="9"/>
-    </row>
-    <row r="6" spans="1:6" ht="81.75" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A6" s="6" t="s">
+    </row>
+    <row r="6" spans="1:5" ht="81.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A6" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="B6" s="6" t="s">
+      <c r="B6" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="C6" s="7" t="s">
+      <c r="C6" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="D6" s="7" t="s">
+      <c r="D6" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="E6" s="8"/>
-    </row>
-    <row r="7" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A7" s="6"/>
-      <c r="B7" s="6"/>
-      <c r="C7" s="7"/>
-      <c r="D7" s="7"/>
-      <c r="E7" s="6"/>
-    </row>
-    <row r="8" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A8" s="6"/>
-      <c r="B8" s="6"/>
-      <c r="C8" s="7"/>
-      <c r="D8" s="7"/>
-      <c r="E8" s="6"/>
-    </row>
-    <row r="9" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A9" s="6"/>
-      <c r="B9" s="6"/>
-      <c r="C9" s="7"/>
-      <c r="D9" s="7"/>
-      <c r="E9" s="6"/>
-    </row>
-    <row r="10" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A10" s="6"/>
-      <c r="B10" s="6"/>
-      <c r="C10" s="7"/>
-      <c r="D10" s="7"/>
-      <c r="E10" s="6"/>
-    </row>
-    <row r="11" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A11" s="6"/>
-      <c r="B11" s="6"/>
-      <c r="C11" s="7"/>
-      <c r="D11" s="7"/>
-      <c r="E11" s="6"/>
-    </row>
-    <row r="12" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A12" s="6"/>
-      <c r="B12" s="6"/>
-      <c r="C12" s="7"/>
-      <c r="D12" s="7"/>
-      <c r="E12" s="6"/>
-    </row>
-    <row r="13" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A13" s="6"/>
-      <c r="B13" s="6"/>
-      <c r="C13" s="7"/>
-      <c r="D13" s="7"/>
-      <c r="E13" s="6"/>
-    </row>
-    <row r="14" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A14" s="6"/>
-      <c r="B14" s="6"/>
-      <c r="C14" s="7"/>
-      <c r="D14" s="7"/>
-      <c r="E14" s="6"/>
-    </row>
-    <row r="15" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A15" s="6"/>
-      <c r="B15" s="6"/>
-      <c r="C15" s="7"/>
-      <c r="D15" s="7"/>
-      <c r="E15" s="6"/>
-    </row>
-    <row r="16" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="E6" s="9"/>
+    </row>
+    <row r="7" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A7" s="7"/>
+      <c r="B7" s="7"/>
+      <c r="C7" s="8"/>
+      <c r="D7" s="8"/>
+      <c r="E7" s="7"/>
+    </row>
+    <row r="8" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A8" s="7"/>
+      <c r="B8" s="7"/>
+      <c r="C8" s="8"/>
+      <c r="D8" s="8"/>
+      <c r="E8" s="7"/>
+    </row>
+    <row r="9" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A9" s="7"/>
+      <c r="B9" s="7"/>
+      <c r="C9" s="8"/>
+      <c r="D9" s="8"/>
+      <c r="E9" s="7"/>
+    </row>
+    <row r="10" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A10" s="7"/>
+      <c r="B10" s="7"/>
+      <c r="C10" s="8"/>
+      <c r="D10" s="8"/>
+      <c r="E10" s="7"/>
+    </row>
+    <row r="11" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A11" s="7"/>
+      <c r="B11" s="7"/>
+      <c r="C11" s="8"/>
+      <c r="D11" s="8"/>
+      <c r="E11" s="7"/>
+    </row>
+    <row r="12" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A12" s="7"/>
+      <c r="B12" s="7"/>
+      <c r="C12" s="8"/>
+      <c r="D12" s="8"/>
+      <c r="E12" s="7"/>
+    </row>
+    <row r="13" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A13" s="7"/>
+      <c r="B13" s="7"/>
+      <c r="C13" s="8"/>
+      <c r="D13" s="8"/>
+      <c r="E13" s="7"/>
+    </row>
+    <row r="14" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A14" s="7"/>
+      <c r="B14" s="7"/>
+      <c r="C14" s="8"/>
+      <c r="D14" s="8"/>
+      <c r="E14" s="7"/>
+    </row>
+    <row r="15" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A15" s="7"/>
+      <c r="B15" s="7"/>
+      <c r="C15" s="8"/>
+      <c r="D15" s="8"/>
+      <c r="E15" s="7"/>
+    </row>
+    <row r="16" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A16" s="1" t="s">
         <v>22</v>
       </c>
@@ -1077,7 +1111,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="17" spans="1:5" ht="249" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:5" ht="249" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A17" s="3" t="s">
         <v>27</v>
       </c>
@@ -1094,10 +1128,24 @@
         <v>31</v>
       </c>
     </row>
-    <row r="18" spans="1:5" ht="80.25" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="C18" s="4"/>
-    </row>
-    <row r="19" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="18" spans="1:5" ht="80.25" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A18" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="B18" t="s">
+        <v>14</v>
+      </c>
+      <c r="C18" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="D18" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="E18" s="4" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
   </sheetData>
   <mergeCells count="5">
     <mergeCell ref="A6:A15"/>

--- a/materials/設計ドキュメント.xlsx
+++ b/materials/設計ドキュメント.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\篠崎心寧\Desktop\team03\materials\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D084DE1C-4937-4B72-A096-298D6A45EB07}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{983E034A-633E-46A5-A934-54F2C799F9EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="9510" yWindow="0" windowWidth="9780" windowHeight="10170" xr2:uid="{8691A593-23F5-4A86-9C44-944ADFFAF4A8}"/>
   </bookViews>
@@ -327,14 +327,6 @@
     <t>登録されている全企業データ（companies）</t>
   </si>
   <si>
-    <t>新規企業を追加する（add）
-既存企業を更新する（update）
-企業を削除する（remove）
-企業名で検索する（searchByName）
-全件取得する（getAll）
-締切が近い順に並べ替える（sortByNearestDeadline）</t>
-  </si>
-  <si>
     <t>企業の全データはCompanyRepositoryクラス（別行）を参照。
 検索・削除もCompanyRepository側のメソッドを呼び出す想定。</t>
   </si>
@@ -446,6 +438,15 @@
 同じ処理を繰り返すことに気づき、共通クラスとして分離した。
 特定の画面に属さない汎用部品のため、カレンダー画面の「予定を追加」欄など
 他の画面でも再利用できる可能性がある。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>新規企業を追加する（add）
+既存企業を更新する（update）
+企業を削除する（remove）
+企業名で検索する（searchByName）
+全件取得する（getAll）
+締切が近い順に並べ替える（sortByNearestDeadline）</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -577,6 +578,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
@@ -584,9 +588,6 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -979,7 +980,7 @@
         <v>12</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="180" x14ac:dyDescent="0.55000000000000004">
@@ -996,7 +997,7 @@
         <v>16</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="50.25" customHeight="1" x14ac:dyDescent="0.55000000000000004">
@@ -1013,86 +1014,86 @@
         <v>19</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="81.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A6" s="7" t="s">
+      <c r="A6" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="B6" s="7" t="s">
+      <c r="B6" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="C6" s="8" t="s">
+      <c r="C6" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="D6" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="E6" s="9"/>
+      <c r="D6" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="E6" s="10"/>
     </row>
     <row r="7" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A7" s="7"/>
-      <c r="B7" s="7"/>
-      <c r="C7" s="8"/>
-      <c r="D7" s="8"/>
-      <c r="E7" s="7"/>
+      <c r="A7" s="8"/>
+      <c r="B7" s="8"/>
+      <c r="C7" s="9"/>
+      <c r="D7" s="9"/>
+      <c r="E7" s="8"/>
     </row>
     <row r="8" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A8" s="7"/>
-      <c r="B8" s="7"/>
-      <c r="C8" s="8"/>
-      <c r="D8" s="8"/>
-      <c r="E8" s="7"/>
+      <c r="A8" s="8"/>
+      <c r="B8" s="8"/>
+      <c r="C8" s="9"/>
+      <c r="D8" s="9"/>
+      <c r="E8" s="8"/>
     </row>
     <row r="9" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A9" s="7"/>
-      <c r="B9" s="7"/>
-      <c r="C9" s="8"/>
-      <c r="D9" s="8"/>
-      <c r="E9" s="7"/>
+      <c r="A9" s="8"/>
+      <c r="B9" s="8"/>
+      <c r="C9" s="9"/>
+      <c r="D9" s="9"/>
+      <c r="E9" s="8"/>
     </row>
     <row r="10" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A10" s="7"/>
-      <c r="B10" s="7"/>
-      <c r="C10" s="8"/>
-      <c r="D10" s="8"/>
-      <c r="E10" s="7"/>
+      <c r="A10" s="8"/>
+      <c r="B10" s="8"/>
+      <c r="C10" s="9"/>
+      <c r="D10" s="9"/>
+      <c r="E10" s="8"/>
     </row>
     <row r="11" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A11" s="7"/>
-      <c r="B11" s="7"/>
-      <c r="C11" s="8"/>
-      <c r="D11" s="8"/>
-      <c r="E11" s="7"/>
+      <c r="A11" s="8"/>
+      <c r="B11" s="8"/>
+      <c r="C11" s="9"/>
+      <c r="D11" s="9"/>
+      <c r="E11" s="8"/>
     </row>
     <row r="12" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A12" s="7"/>
-      <c r="B12" s="7"/>
-      <c r="C12" s="8"/>
-      <c r="D12" s="8"/>
-      <c r="E12" s="7"/>
+      <c r="A12" s="8"/>
+      <c r="B12" s="8"/>
+      <c r="C12" s="9"/>
+      <c r="D12" s="9"/>
+      <c r="E12" s="8"/>
     </row>
     <row r="13" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A13" s="7"/>
-      <c r="B13" s="7"/>
-      <c r="C13" s="8"/>
-      <c r="D13" s="8"/>
-      <c r="E13" s="7"/>
+      <c r="A13" s="8"/>
+      <c r="B13" s="8"/>
+      <c r="C13" s="9"/>
+      <c r="D13" s="9"/>
+      <c r="E13" s="8"/>
     </row>
     <row r="14" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A14" s="7"/>
-      <c r="B14" s="7"/>
-      <c r="C14" s="8"/>
-      <c r="D14" s="8"/>
-      <c r="E14" s="7"/>
+      <c r="A14" s="8"/>
+      <c r="B14" s="8"/>
+      <c r="C14" s="9"/>
+      <c r="D14" s="9"/>
+      <c r="E14" s="8"/>
     </row>
     <row r="15" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A15" s="7"/>
-      <c r="B15" s="7"/>
-      <c r="C15" s="8"/>
-      <c r="D15" s="8"/>
-      <c r="E15" s="7"/>
+      <c r="A15" s="8"/>
+      <c r="B15" s="8"/>
+      <c r="C15" s="9"/>
+      <c r="D15" s="9"/>
+      <c r="E15" s="8"/>
     </row>
     <row r="16" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A16" s="1" t="s">
@@ -1122,27 +1123,27 @@
         <v>28</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="18" spans="1:5" ht="80.25" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A18" s="10" t="s">
-        <v>35</v>
+      <c r="A18" s="7" t="s">
+        <v>34</v>
       </c>
       <c r="B18" t="s">
         <v>14</v>
       </c>
       <c r="C18" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="D18" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="D18" s="4" t="s">
+      <c r="E18" s="4" t="s">
         <v>37</v>
-      </c>
-      <c r="E18" s="4" t="s">
-        <v>38</v>
       </c>
     </row>
     <row r="19" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
